--- a/data/gravel/Scott Scale RC 2025.xlsx
+++ b/data/gravel/Scott Scale RC 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64584C3D-7B4C-DE4C-B66F-D5B89C5E01CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3DAC9E-AB5B-5747-AB68-E9A32F470363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32440" yWindow="-20440" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
